--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4376B4C-BF70-487F-A8CA-ADB2885D6B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF22E176-1ABB-4B70-AD27-6F1E3F59714B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,69 +20,273 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-032383</t>
-  </si>
-  <si>
-    <t>LP-044468</t>
-  </si>
-  <si>
-    <t>LP-047127</t>
-  </si>
-  <si>
-    <t>LP-047276</t>
-  </si>
-  <si>
-    <t>LP-047425</t>
-  </si>
-  <si>
-    <t>LP-047636</t>
-  </si>
-  <si>
-    <t>LP-048244</t>
-  </si>
-  <si>
-    <t>LP-048301</t>
-  </si>
-  <si>
-    <t>LP-048670</t>
-  </si>
-  <si>
-    <t>LP-048674</t>
-  </si>
-  <si>
-    <t>LP-048746</t>
-  </si>
-  <si>
-    <t>LP-048932</t>
-  </si>
-  <si>
-    <t>LP-049427</t>
-  </si>
-  <si>
-    <t>LP-049443</t>
-  </si>
-  <si>
-    <t>LP-049800</t>
-  </si>
-  <si>
-    <t>LP-050182</t>
-  </si>
-  <si>
-    <t>LP-050183</t>
-  </si>
-  <si>
-    <t>LP-050208</t>
-  </si>
-  <si>
-    <t>LP-043257</t>
-  </si>
-  <si>
-    <t>LP-049257</t>
+    <t>LP-044591</t>
+  </si>
+  <si>
+    <t>LP-044706</t>
+  </si>
+  <si>
+    <t>LP-045075</t>
+  </si>
+  <si>
+    <t>LP-045879</t>
+  </si>
+  <si>
+    <t>LP-047121</t>
+  </si>
+  <si>
+    <t>LP-047129</t>
+  </si>
+  <si>
+    <t>LP-047395</t>
+  </si>
+  <si>
+    <t>LP-047427</t>
+  </si>
+  <si>
+    <t>LP-047464</t>
+  </si>
+  <si>
+    <t>LP-047893</t>
+  </si>
+  <si>
+    <t>LP-047905</t>
+  </si>
+  <si>
+    <t>LP-047962</t>
+  </si>
+  <si>
+    <t>LP-047998</t>
+  </si>
+  <si>
+    <t>LP-048003</t>
+  </si>
+  <si>
+    <t>LP-048022</t>
+  </si>
+  <si>
+    <t>LP-048023</t>
+  </si>
+  <si>
+    <t>LP-048063</t>
+  </si>
+  <si>
+    <t>LP-048086</t>
+  </si>
+  <si>
+    <t>LP-048303</t>
+  </si>
+  <si>
+    <t>LP-048305</t>
+  </si>
+  <si>
+    <t>LP-048306</t>
+  </si>
+  <si>
+    <t>LP-048322</t>
+  </si>
+  <si>
+    <t>LP-048323</t>
+  </si>
+  <si>
+    <t>LP-048437</t>
+  </si>
+  <si>
+    <t>LP-048447</t>
+  </si>
+  <si>
+    <t>LP-048470</t>
+  </si>
+  <si>
+    <t>LP-048540</t>
+  </si>
+  <si>
+    <t>LP-048720</t>
+  </si>
+  <si>
+    <t>LP-048724</t>
+  </si>
+  <si>
+    <t>LP-048727</t>
+  </si>
+  <si>
+    <t>LP-048752</t>
+  </si>
+  <si>
+    <t>LP-048858</t>
+  </si>
+  <si>
+    <t>LP-048900</t>
+  </si>
+  <si>
+    <t>LP-048956</t>
+  </si>
+  <si>
+    <t>LP-048957</t>
+  </si>
+  <si>
+    <t>LP-049011</t>
+  </si>
+  <si>
+    <t>LP-049022</t>
+  </si>
+  <si>
+    <t>LP-049085</t>
+  </si>
+  <si>
+    <t>LP-049126</t>
+  </si>
+  <si>
+    <t>LP-049240</t>
+  </si>
+  <si>
+    <t>LP-049252</t>
+  </si>
+  <si>
+    <t>LP-049265</t>
+  </si>
+  <si>
+    <t>LP-049404</t>
+  </si>
+  <si>
+    <t>LP-049413</t>
+  </si>
+  <si>
+    <t>LP-049414</t>
+  </si>
+  <si>
+    <t>LP-049425</t>
+  </si>
+  <si>
+    <t>LP-049428</t>
+  </si>
+  <si>
+    <t>LP-049436</t>
+  </si>
+  <si>
+    <t>LP-049447</t>
+  </si>
+  <si>
+    <t>LP-049476</t>
+  </si>
+  <si>
+    <t>LP-049514</t>
+  </si>
+  <si>
+    <t>LP-049552</t>
+  </si>
+  <si>
+    <t>LP-049656</t>
+  </si>
+  <si>
+    <t>LP-049679</t>
+  </si>
+  <si>
+    <t>LP-049687</t>
+  </si>
+  <si>
+    <t>LP-049696</t>
+  </si>
+  <si>
+    <t>LP-049699</t>
+  </si>
+  <si>
+    <t>LP-049700</t>
+  </si>
+  <si>
+    <t>LP-049710</t>
+  </si>
+  <si>
+    <t>LP-049712</t>
+  </si>
+  <si>
+    <t>LP-049717</t>
+  </si>
+  <si>
+    <t>LP-049724</t>
+  </si>
+  <si>
+    <t>LP-049725</t>
+  </si>
+  <si>
+    <t>LP-049751</t>
+  </si>
+  <si>
+    <t>LP-049807</t>
+  </si>
+  <si>
+    <t>LP-049810</t>
+  </si>
+  <si>
+    <t>LP-049868</t>
+  </si>
+  <si>
+    <t>LP-049921</t>
+  </si>
+  <si>
+    <t>LP-049922</t>
+  </si>
+  <si>
+    <t>LP-049928</t>
+  </si>
+  <si>
+    <t>LP-049929</t>
+  </si>
+  <si>
+    <t>LP-049977</t>
+  </si>
+  <si>
+    <t>LP-049979</t>
+  </si>
+  <si>
+    <t>LP-050011</t>
+  </si>
+  <si>
+    <t>LP-050037</t>
+  </si>
+  <si>
+    <t>LP-050062</t>
+  </si>
+  <si>
+    <t>LP-050075</t>
+  </si>
+  <si>
+    <t>LP-050162</t>
+  </si>
+  <si>
+    <t>LP-050169</t>
+  </si>
+  <si>
+    <t>LP-050266</t>
+  </si>
+  <si>
+    <t>LP-050316</t>
+  </si>
+  <si>
+    <t>LP-050323</t>
+  </si>
+  <si>
+    <t>LP-050354</t>
+  </si>
+  <si>
+    <t>LP-050373</t>
+  </si>
+  <si>
+    <t>LP-048324</t>
+  </si>
+  <si>
+    <t>LP-048813</t>
+  </si>
+  <si>
+    <t>LP-049418</t>
+  </si>
+  <si>
+    <t>LP-049520</t>
   </si>
 </sst>
 </file>
@@ -445,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -463,97 +667,437 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,102 +8,223 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E3E0D8-BFCC-4314-98F4-A95FAFA78A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE914091-86DA-4509-A3A0-66B174D0281C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-047288</t>
-  </si>
-  <si>
-    <t>LP-047289</t>
-  </si>
-  <si>
-    <t>LP-047922</t>
-  </si>
-  <si>
-    <t>LP-048949</t>
-  </si>
-  <si>
-    <t>LP-049086</t>
-  </si>
-  <si>
-    <t>LP-049241</t>
-  </si>
-  <si>
-    <t>LP-049439</t>
-  </si>
-  <si>
-    <t>LP-048498</t>
-  </si>
-  <si>
-    <t>LP-049711</t>
-  </si>
-  <si>
-    <t>LP-049794</t>
-  </si>
-  <si>
-    <t>LP-049866</t>
-  </si>
-  <si>
-    <t>LP-049900</t>
-  </si>
-  <si>
-    <t>LP-049906</t>
-  </si>
-  <si>
-    <t>LP-049944</t>
-  </si>
-  <si>
-    <t>LP-049978</t>
-  </si>
-  <si>
-    <t>LP-050051</t>
-  </si>
-  <si>
-    <t>LP-050067</t>
-  </si>
-  <si>
-    <t>LP-050102</t>
-  </si>
-  <si>
-    <t>LP-050168</t>
-  </si>
-  <si>
-    <t>LP-050266</t>
-  </si>
-  <si>
-    <t>LP-050286</t>
-  </si>
-  <si>
-    <t>LP-050489</t>
-  </si>
-  <si>
-    <t>LP-050542</t>
-  </si>
-  <si>
-    <t>LP-050577</t>
-  </si>
-  <si>
-    <t>LP-049980</t>
-  </si>
-  <si>
-    <t>LP-050072</t>
-  </si>
-  <si>
-    <t>LP-050118</t>
+    <t>LP-036424</t>
+  </si>
+  <si>
+    <t>LP-037582</t>
+  </si>
+  <si>
+    <t>LP-042263</t>
+  </si>
+  <si>
+    <t>LP-043885</t>
+  </si>
+  <si>
+    <t>LP-043986</t>
+  </si>
+  <si>
+    <t>LP-043987</t>
+  </si>
+  <si>
+    <t>LP-043988</t>
+  </si>
+  <si>
+    <t>LP-043990</t>
+  </si>
+  <si>
+    <t>LP-043991</t>
+  </si>
+  <si>
+    <t>LP-043992</t>
+  </si>
+  <si>
+    <t>LP-044475</t>
+  </si>
+  <si>
+    <t>LP-045420</t>
+  </si>
+  <si>
+    <t>LP-046106</t>
+  </si>
+  <si>
+    <t>LP-046496</t>
+  </si>
+  <si>
+    <t>LP-047202</t>
+  </si>
+  <si>
+    <t>LP-047995</t>
+  </si>
+  <si>
+    <t>LP-048078</t>
+  </si>
+  <si>
+    <t>LP-048238</t>
+  </si>
+  <si>
+    <t>LP-048333</t>
+  </si>
+  <si>
+    <t>LP-048354</t>
+  </si>
+  <si>
+    <t>LP-048532</t>
+  </si>
+  <si>
+    <t>LP-048590</t>
+  </si>
+  <si>
+    <t>LP-048592</t>
+  </si>
+  <si>
+    <t>LP-049071</t>
+  </si>
+  <si>
+    <t>LP-049078</t>
+  </si>
+  <si>
+    <t>LP-049080</t>
+  </si>
+  <si>
+    <t>LP-049258</t>
+  </si>
+  <si>
+    <t>LP-049259</t>
+  </si>
+  <si>
+    <t>LP-049260</t>
+  </si>
+  <si>
+    <t>LP-049372</t>
+  </si>
+  <si>
+    <t>LP-049397</t>
+  </si>
+  <si>
+    <t>LP-049410</t>
+  </si>
+  <si>
+    <t>LP-049411</t>
+  </si>
+  <si>
+    <t>LP-049419</t>
+  </si>
+  <si>
+    <t>LP-049446</t>
+  </si>
+  <si>
+    <t>LP-049549</t>
+  </si>
+  <si>
+    <t>LP-049550</t>
+  </si>
+  <si>
+    <t>LP-049553</t>
+  </si>
+  <si>
+    <t>LP-049554</t>
+  </si>
+  <si>
+    <t>LP-049685</t>
+  </si>
+  <si>
+    <t>LP-049723</t>
+  </si>
+  <si>
+    <t>LP-049774</t>
+  </si>
+  <si>
+    <t>LP-049776</t>
+  </si>
+  <si>
+    <t>LP-049968</t>
+  </si>
+  <si>
+    <t>LP-050055</t>
+  </si>
+  <si>
+    <t>LP-050060</t>
+  </si>
+  <si>
+    <t>LP-050071</t>
+  </si>
+  <si>
+    <t>LP-050145</t>
+  </si>
+  <si>
+    <t>LP-050152</t>
+  </si>
+  <si>
+    <t>LP-050135</t>
+  </si>
+  <si>
+    <t>LP-050314</t>
+  </si>
+  <si>
+    <t>LP-050322</t>
+  </si>
+  <si>
+    <t>LP-050331</t>
+  </si>
+  <si>
+    <t>LP-050351</t>
+  </si>
+  <si>
+    <t>LP-050504</t>
+  </si>
+  <si>
+    <t>LP-050576</t>
+  </si>
+  <si>
+    <t>LP-050591</t>
+  </si>
+  <si>
+    <t>LP-047156</t>
+  </si>
+  <si>
+    <t>LP-047412</t>
+  </si>
+  <si>
+    <t>LP-048449</t>
+  </si>
+  <si>
+    <t>LP-049420</t>
+  </si>
+  <si>
+    <t>LP-049838</t>
+  </si>
+  <si>
+    <t>LP-050004</t>
   </si>
 </sst>
 </file>
@@ -466,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -549,47 +670,47 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -610,6 +731,186 @@
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,223 +8,192 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE914091-86DA-4509-A3A0-66B174D0281C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846C579A-E736-407B-B775-091B4A9EE1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-036424</t>
-  </si>
-  <si>
-    <t>LP-037582</t>
-  </si>
-  <si>
-    <t>LP-042263</t>
-  </si>
-  <si>
-    <t>LP-043885</t>
-  </si>
-  <si>
-    <t>LP-043986</t>
-  </si>
-  <si>
-    <t>LP-043987</t>
-  </si>
-  <si>
-    <t>LP-043988</t>
-  </si>
-  <si>
-    <t>LP-043990</t>
-  </si>
-  <si>
-    <t>LP-043991</t>
-  </si>
-  <si>
-    <t>LP-043992</t>
-  </si>
-  <si>
-    <t>LP-044475</t>
-  </si>
-  <si>
-    <t>LP-045420</t>
-  </si>
-  <si>
-    <t>LP-046106</t>
-  </si>
-  <si>
-    <t>LP-046496</t>
-  </si>
-  <si>
-    <t>LP-047202</t>
-  </si>
-  <si>
-    <t>LP-047995</t>
-  </si>
-  <si>
-    <t>LP-048078</t>
-  </si>
-  <si>
-    <t>LP-048238</t>
-  </si>
-  <si>
-    <t>LP-048333</t>
-  </si>
-  <si>
-    <t>LP-048354</t>
-  </si>
-  <si>
-    <t>LP-048532</t>
-  </si>
-  <si>
-    <t>LP-048590</t>
-  </si>
-  <si>
-    <t>LP-048592</t>
-  </si>
-  <si>
-    <t>LP-049071</t>
-  </si>
-  <si>
-    <t>LP-049078</t>
-  </si>
-  <si>
-    <t>LP-049080</t>
-  </si>
-  <si>
-    <t>LP-049258</t>
-  </si>
-  <si>
-    <t>LP-049259</t>
-  </si>
-  <si>
-    <t>LP-049260</t>
-  </si>
-  <si>
-    <t>LP-049372</t>
-  </si>
-  <si>
-    <t>LP-049397</t>
-  </si>
-  <si>
-    <t>LP-049410</t>
-  </si>
-  <si>
-    <t>LP-049411</t>
-  </si>
-  <si>
-    <t>LP-049419</t>
-  </si>
-  <si>
-    <t>LP-049446</t>
-  </si>
-  <si>
-    <t>LP-049549</t>
-  </si>
-  <si>
-    <t>LP-049550</t>
-  </si>
-  <si>
-    <t>LP-049553</t>
-  </si>
-  <si>
-    <t>LP-049554</t>
-  </si>
-  <si>
-    <t>LP-049685</t>
-  </si>
-  <si>
-    <t>LP-049723</t>
-  </si>
-  <si>
-    <t>LP-049774</t>
-  </si>
-  <si>
-    <t>LP-049776</t>
-  </si>
-  <si>
-    <t>LP-049968</t>
-  </si>
-  <si>
-    <t>LP-050055</t>
-  </si>
-  <si>
-    <t>LP-050060</t>
-  </si>
-  <si>
-    <t>LP-050071</t>
-  </si>
-  <si>
-    <t>LP-050145</t>
-  </si>
-  <si>
-    <t>LP-050152</t>
-  </si>
-  <si>
-    <t>LP-050135</t>
-  </si>
-  <si>
-    <t>LP-050314</t>
-  </si>
-  <si>
-    <t>LP-050322</t>
-  </si>
-  <si>
-    <t>LP-050331</t>
-  </si>
-  <si>
-    <t>LP-050351</t>
-  </si>
-  <si>
-    <t>LP-050504</t>
-  </si>
-  <si>
-    <t>LP-050576</t>
-  </si>
-  <si>
-    <t>LP-050591</t>
-  </si>
-  <si>
-    <t>LP-047156</t>
-  </si>
-  <si>
-    <t>LP-047412</t>
-  </si>
-  <si>
-    <t>LP-048449</t>
-  </si>
-  <si>
-    <t>LP-049420</t>
-  </si>
-  <si>
-    <t>LP-049838</t>
-  </si>
-  <si>
-    <t>LP-050004</t>
+    <t>LP-042605</t>
+  </si>
+  <si>
+    <t>LP-045880</t>
+  </si>
+  <si>
+    <t>LP-046158</t>
+  </si>
+  <si>
+    <t>LP-048214</t>
+  </si>
+  <si>
+    <t>LP-048388</t>
+  </si>
+  <si>
+    <t>LP-048523</t>
+  </si>
+  <si>
+    <t>LP-048524</t>
+  </si>
+  <si>
+    <t>LP-048853</t>
+  </si>
+  <si>
+    <t>LP-048852</t>
+  </si>
+  <si>
+    <t>LP-048995</t>
+  </si>
+  <si>
+    <t>LP-049083</t>
+  </si>
+  <si>
+    <t>LP-049171</t>
+  </si>
+  <si>
+    <t>LP-049174</t>
+  </si>
+  <si>
+    <t>LP-049233</t>
+  </si>
+  <si>
+    <t>LP-049294</t>
+  </si>
+  <si>
+    <t>LP-049537</t>
+  </si>
+  <si>
+    <t>LP-049557</t>
+  </si>
+  <si>
+    <t>LP-049592</t>
+  </si>
+  <si>
+    <t>LP-049713</t>
+  </si>
+  <si>
+    <t>LP-049719</t>
+  </si>
+  <si>
+    <t>LP-049802</t>
+  </si>
+  <si>
+    <t>LP-049808</t>
+  </si>
+  <si>
+    <t>LP-049869</t>
+  </si>
+  <si>
+    <t>LP-049925</t>
+  </si>
+  <si>
+    <t>LP-049926</t>
+  </si>
+  <si>
+    <t>LP-049927</t>
+  </si>
+  <si>
+    <t>LP-049949</t>
+  </si>
+  <si>
+    <t>LP-050022</t>
+  </si>
+  <si>
+    <t>LP-050101</t>
+  </si>
+  <si>
+    <t>LP-050221</t>
+  </si>
+  <si>
+    <t>LP-050288</t>
+  </si>
+  <si>
+    <t>LP-050289</t>
+  </si>
+  <si>
+    <t>LP-050291</t>
+  </si>
+  <si>
+    <t>LP-050306</t>
+  </si>
+  <si>
+    <t>LP-050307</t>
+  </si>
+  <si>
+    <t>LP-050329</t>
+  </si>
+  <si>
+    <t>LP-050340</t>
+  </si>
+  <si>
+    <t>LP-050346</t>
+  </si>
+  <si>
+    <t>LP-050362</t>
+  </si>
+  <si>
+    <t>LP-050481</t>
+  </si>
+  <si>
+    <t>LP-050492</t>
+  </si>
+  <si>
+    <t>LP-050558</t>
+  </si>
+  <si>
+    <t>LP-050559</t>
+  </si>
+  <si>
+    <t>LP-050575</t>
+  </si>
+  <si>
+    <t>LP-050843</t>
+  </si>
+  <si>
+    <t>LP-049176</t>
+  </si>
+  <si>
+    <t>LP-049701</t>
+  </si>
+  <si>
+    <t>LP-049920</t>
+  </si>
+  <si>
+    <t>LP-049951</t>
+  </si>
+  <si>
+    <t>LP-049981</t>
+  </si>
+  <si>
+    <t>LP-049986</t>
+  </si>
+  <si>
+    <t>LP-050074</t>
+  </si>
+  <si>
+    <t>LP-050107</t>
+  </si>
+  <si>
+    <t>LP-050265</t>
+  </si>
+  <si>
+    <t>LP-050295</t>
+  </si>
+  <si>
+    <t>LP-050330</t>
+  </si>
+  <si>
+    <t>LP-050345</t>
   </si>
 </sst>
 </file>
@@ -587,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -665,12 +634,12 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -680,22 +649,22 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -710,22 +679,22 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
@@ -750,167 +719,137 @@
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846C579A-E736-407B-B775-091B4A9EE1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FC89BB-F10D-487D-A113-992DF4116799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,180 +20,279 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-042605</t>
-  </si>
-  <si>
-    <t>LP-045880</t>
-  </si>
-  <si>
-    <t>LP-046158</t>
-  </si>
-  <si>
-    <t>LP-048214</t>
-  </si>
-  <si>
-    <t>LP-048388</t>
-  </si>
-  <si>
-    <t>LP-048523</t>
-  </si>
-  <si>
-    <t>LP-048524</t>
-  </si>
-  <si>
-    <t>LP-048853</t>
-  </si>
-  <si>
-    <t>LP-048852</t>
-  </si>
-  <si>
-    <t>LP-048995</t>
-  </si>
-  <si>
-    <t>LP-049083</t>
-  </si>
-  <si>
-    <t>LP-049171</t>
-  </si>
-  <si>
-    <t>LP-049174</t>
-  </si>
-  <si>
-    <t>LP-049233</t>
-  </si>
-  <si>
-    <t>LP-049294</t>
-  </si>
-  <si>
-    <t>LP-049537</t>
-  </si>
-  <si>
-    <t>LP-049557</t>
-  </si>
-  <si>
-    <t>LP-049592</t>
-  </si>
-  <si>
-    <t>LP-049713</t>
-  </si>
-  <si>
-    <t>LP-049719</t>
-  </si>
-  <si>
-    <t>LP-049802</t>
-  </si>
-  <si>
-    <t>LP-049808</t>
-  </si>
-  <si>
-    <t>LP-049869</t>
-  </si>
-  <si>
-    <t>LP-049925</t>
-  </si>
-  <si>
-    <t>LP-049926</t>
-  </si>
-  <si>
-    <t>LP-049927</t>
-  </si>
-  <si>
-    <t>LP-049949</t>
-  </si>
-  <si>
-    <t>LP-050022</t>
-  </si>
-  <si>
-    <t>LP-050101</t>
-  </si>
-  <si>
-    <t>LP-050221</t>
-  </si>
-  <si>
-    <t>LP-050288</t>
-  </si>
-  <si>
-    <t>LP-050289</t>
-  </si>
-  <si>
-    <t>LP-050291</t>
-  </si>
-  <si>
-    <t>LP-050306</t>
-  </si>
-  <si>
-    <t>LP-050307</t>
-  </si>
-  <si>
-    <t>LP-050329</t>
-  </si>
-  <si>
-    <t>LP-050340</t>
-  </si>
-  <si>
-    <t>LP-050346</t>
-  </si>
-  <si>
-    <t>LP-050362</t>
-  </si>
-  <si>
-    <t>LP-050481</t>
-  </si>
-  <si>
-    <t>LP-050492</t>
-  </si>
-  <si>
-    <t>LP-050558</t>
-  </si>
-  <si>
-    <t>LP-050559</t>
-  </si>
-  <si>
-    <t>LP-050575</t>
-  </si>
-  <si>
-    <t>LP-050843</t>
-  </si>
-  <si>
-    <t>LP-049176</t>
-  </si>
-  <si>
-    <t>LP-049701</t>
-  </si>
-  <si>
-    <t>LP-049920</t>
-  </si>
-  <si>
-    <t>LP-049951</t>
-  </si>
-  <si>
-    <t>LP-049981</t>
-  </si>
-  <si>
-    <t>LP-049986</t>
-  </si>
-  <si>
-    <t>LP-050074</t>
-  </si>
-  <si>
-    <t>LP-050107</t>
-  </si>
-  <si>
-    <t>LP-050265</t>
-  </si>
-  <si>
-    <t>LP-050295</t>
-  </si>
-  <si>
-    <t>LP-050330</t>
-  </si>
-  <si>
-    <t>LP-050345</t>
+    <t>LP-047084</t>
+  </si>
+  <si>
+    <t>LP-047280</t>
+  </si>
+  <si>
+    <t>LP-047413</t>
+  </si>
+  <si>
+    <t>LP-047414</t>
+  </si>
+  <si>
+    <t>LP-047966</t>
+  </si>
+  <si>
+    <t>LP-047967</t>
+  </si>
+  <si>
+    <t>LP-047969</t>
+  </si>
+  <si>
+    <t>LP-047973</t>
+  </si>
+  <si>
+    <t>LP-047974</t>
+  </si>
+  <si>
+    <t>LP-048027</t>
+  </si>
+  <si>
+    <t>LP-048041</t>
+  </si>
+  <si>
+    <t>LP-048076</t>
+  </si>
+  <si>
+    <t>LP-048239</t>
+  </si>
+  <si>
+    <t>LP-048319</t>
+  </si>
+  <si>
+    <t>LP-048525</t>
+  </si>
+  <si>
+    <t>LP-048546</t>
+  </si>
+  <si>
+    <t>LP-048576</t>
+  </si>
+  <si>
+    <t>LP-048591</t>
+  </si>
+  <si>
+    <t>LP-048593</t>
+  </si>
+  <si>
+    <t>LP-048594</t>
+  </si>
+  <si>
+    <t>LP-048595</t>
+  </si>
+  <si>
+    <t>LP-048596</t>
+  </si>
+  <si>
+    <t>LP-048645</t>
+  </si>
+  <si>
+    <t>LP-048655</t>
+  </si>
+  <si>
+    <t>LP-048712</t>
+  </si>
+  <si>
+    <t>LP-048859</t>
+  </si>
+  <si>
+    <t>LP-048902</t>
+  </si>
+  <si>
+    <t>LP-049062</t>
+  </si>
+  <si>
+    <t>LP-049063</t>
+  </si>
+  <si>
+    <t>LP-049064</t>
+  </si>
+  <si>
+    <t>LP-049065</t>
+  </si>
+  <si>
+    <t>LP-049066</t>
+  </si>
+  <si>
+    <t>LP-049068</t>
+  </si>
+  <si>
+    <t>LP-049069</t>
+  </si>
+  <si>
+    <t>LP-049070</t>
+  </si>
+  <si>
+    <t>LP-049072</t>
+  </si>
+  <si>
+    <t>LP-049079</t>
+  </si>
+  <si>
+    <t>LP-049082</t>
+  </si>
+  <si>
+    <t>LP-049084</t>
+  </si>
+  <si>
+    <t>LP-049088</t>
+  </si>
+  <si>
+    <t>LP-049090</t>
+  </si>
+  <si>
+    <t>LP-049113</t>
+  </si>
+  <si>
+    <t>LP-049245</t>
+  </si>
+  <si>
+    <t>LP-049301</t>
+  </si>
+  <si>
+    <t>LP-049302</t>
+  </si>
+  <si>
+    <t>LP-049303</t>
+  </si>
+  <si>
+    <t>LP-049496</t>
+  </si>
+  <si>
+    <t>LP-049498</t>
+  </si>
+  <si>
+    <t>LP-049775</t>
+  </si>
+  <si>
+    <t>LP-049778</t>
+  </si>
+  <si>
+    <t>LP-049817</t>
+  </si>
+  <si>
+    <t>LP-049886</t>
+  </si>
+  <si>
+    <t>LP-049894</t>
+  </si>
+  <si>
+    <t>LP-049916</t>
+  </si>
+  <si>
+    <t>LP-049988</t>
+  </si>
+  <si>
+    <t>LP-050063</t>
+  </si>
+  <si>
+    <t>LP-050076</t>
+  </si>
+  <si>
+    <t>LP-050677</t>
+  </si>
+  <si>
+    <t>LP-050078</t>
+  </si>
+  <si>
+    <t>LP-050079</t>
+  </si>
+  <si>
+    <t>LP-050080</t>
+  </si>
+  <si>
+    <t>LP-050178</t>
+  </si>
+  <si>
+    <t>LP-050201</t>
+  </si>
+  <si>
+    <t>LP-050321</t>
+  </si>
+  <si>
+    <t>LP-050495</t>
+  </si>
+  <si>
+    <t>LP-050497</t>
+  </si>
+  <si>
+    <t>LP-050499</t>
+  </si>
+  <si>
+    <t>LP-050543</t>
+  </si>
+  <si>
+    <t>LP-050638</t>
+  </si>
+  <si>
+    <t>LP-050641</t>
+  </si>
+  <si>
+    <t>LP-050703</t>
+  </si>
+  <si>
+    <t>LP-050807</t>
+  </si>
+  <si>
+    <t>LP-050808</t>
+  </si>
+  <si>
+    <t>LP-050809</t>
+  </si>
+  <si>
+    <t>LP-050810</t>
+  </si>
+  <si>
+    <t>LP-050811</t>
+  </si>
+  <si>
+    <t>LP-050812</t>
+  </si>
+  <si>
+    <t>LP-050846</t>
+  </si>
+  <si>
+    <t>LP-050885</t>
+  </si>
+  <si>
+    <t>LP-050919</t>
+  </si>
+  <si>
+    <t>LP-044259</t>
+  </si>
+  <si>
+    <t>LP-048461</t>
+  </si>
+  <si>
+    <t>LP-048588</t>
+  </si>
+  <si>
+    <t>LP-048657</t>
+  </si>
+  <si>
+    <t>LP-049087</t>
+  </si>
+  <si>
+    <t>LP-049409</t>
+  </si>
+  <si>
+    <t>LP-050081</t>
+  </si>
+  <si>
+    <t>LP-050250</t>
+  </si>
+  <si>
+    <t>LP-050588</t>
+  </si>
+  <si>
+    <t>LP-050704</t>
   </si>
 </sst>
 </file>
@@ -556,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -569,72 +668,72 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -644,57 +743,57 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
@@ -704,152 +803,317 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FC89BB-F10D-487D-A113-992DF4116799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8ACC98-0763-49F2-A8A3-D7FE5D1DB96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,279 +20,300 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-047084</t>
-  </si>
-  <si>
-    <t>LP-047280</t>
-  </si>
-  <si>
-    <t>LP-047413</t>
-  </si>
-  <si>
-    <t>LP-047414</t>
-  </si>
-  <si>
-    <t>LP-047966</t>
-  </si>
-  <si>
-    <t>LP-047967</t>
-  </si>
-  <si>
-    <t>LP-047969</t>
-  </si>
-  <si>
-    <t>LP-047973</t>
-  </si>
-  <si>
-    <t>LP-047974</t>
-  </si>
-  <si>
-    <t>LP-048027</t>
-  </si>
-  <si>
-    <t>LP-048041</t>
-  </si>
-  <si>
-    <t>LP-048076</t>
-  </si>
-  <si>
-    <t>LP-048239</t>
-  </si>
-  <si>
-    <t>LP-048319</t>
-  </si>
-  <si>
-    <t>LP-048525</t>
-  </si>
-  <si>
-    <t>LP-048546</t>
-  </si>
-  <si>
-    <t>LP-048576</t>
-  </si>
-  <si>
-    <t>LP-048591</t>
-  </si>
-  <si>
-    <t>LP-048593</t>
-  </si>
-  <si>
-    <t>LP-048594</t>
-  </si>
-  <si>
-    <t>LP-048595</t>
-  </si>
-  <si>
-    <t>LP-048596</t>
-  </si>
-  <si>
-    <t>LP-048645</t>
-  </si>
-  <si>
-    <t>LP-048655</t>
-  </si>
-  <si>
-    <t>LP-048712</t>
-  </si>
-  <si>
-    <t>LP-048859</t>
-  </si>
-  <si>
-    <t>LP-048902</t>
-  </si>
-  <si>
-    <t>LP-049062</t>
-  </si>
-  <si>
-    <t>LP-049063</t>
-  </si>
-  <si>
-    <t>LP-049064</t>
-  </si>
-  <si>
-    <t>LP-049065</t>
-  </si>
-  <si>
-    <t>LP-049066</t>
-  </si>
-  <si>
-    <t>LP-049068</t>
-  </si>
-  <si>
-    <t>LP-049069</t>
-  </si>
-  <si>
-    <t>LP-049070</t>
-  </si>
-  <si>
-    <t>LP-049072</t>
-  </si>
-  <si>
-    <t>LP-049079</t>
-  </si>
-  <si>
-    <t>LP-049082</t>
-  </si>
-  <si>
-    <t>LP-049084</t>
-  </si>
-  <si>
-    <t>LP-049088</t>
-  </si>
-  <si>
-    <t>LP-049090</t>
-  </si>
-  <si>
-    <t>LP-049113</t>
-  </si>
-  <si>
-    <t>LP-049245</t>
-  </si>
-  <si>
-    <t>LP-049301</t>
-  </si>
-  <si>
-    <t>LP-049302</t>
-  </si>
-  <si>
-    <t>LP-049303</t>
-  </si>
-  <si>
-    <t>LP-049496</t>
-  </si>
-  <si>
-    <t>LP-049498</t>
-  </si>
-  <si>
-    <t>LP-049775</t>
-  </si>
-  <si>
-    <t>LP-049778</t>
-  </si>
-  <si>
-    <t>LP-049817</t>
-  </si>
-  <si>
-    <t>LP-049886</t>
-  </si>
-  <si>
-    <t>LP-049894</t>
-  </si>
-  <si>
-    <t>LP-049916</t>
-  </si>
-  <si>
-    <t>LP-049988</t>
+    <t>LP-041331</t>
+  </si>
+  <si>
+    <t>LP-045379</t>
+  </si>
+  <si>
+    <t>LP-046208</t>
+  </si>
+  <si>
+    <t>LP-046856</t>
+  </si>
+  <si>
+    <t>LP-046871</t>
+  </si>
+  <si>
+    <t>LP-047546</t>
+  </si>
+  <si>
+    <t>LP-047961</t>
+  </si>
+  <si>
+    <t>LP-047994</t>
+  </si>
+  <si>
+    <t>LP-048234</t>
+  </si>
+  <si>
+    <t>LP-048235</t>
+  </si>
+  <si>
+    <t>LP-048237</t>
+  </si>
+  <si>
+    <t>LP-048358</t>
+  </si>
+  <si>
+    <t>LP-048475</t>
+  </si>
+  <si>
+    <t>LP-048483</t>
+  </si>
+  <si>
+    <t>LP-048667</t>
+  </si>
+  <si>
+    <t>LP-048669</t>
+  </si>
+  <si>
+    <t>LP-048689</t>
+  </si>
+  <si>
+    <t>LP-048876</t>
+  </si>
+  <si>
+    <t>LP-048900</t>
+  </si>
+  <si>
+    <t>LP-048977</t>
+  </si>
+  <si>
+    <t>LP-049054</t>
+  </si>
+  <si>
+    <t>LP-049089</t>
+  </si>
+  <si>
+    <t>LP-049144</t>
+  </si>
+  <si>
+    <t>LP-049279</t>
+  </si>
+  <si>
+    <t>LP-049405</t>
+  </si>
+  <si>
+    <t>LP-049408</t>
+  </si>
+  <si>
+    <t>LP-049681</t>
+  </si>
+  <si>
+    <t>LP-049697</t>
+  </si>
+  <si>
+    <t>LP-049698</t>
+  </si>
+  <si>
+    <t>LP-049718</t>
+  </si>
+  <si>
+    <t>LP-049721</t>
+  </si>
+  <si>
+    <t>LP-049722</t>
+  </si>
+  <si>
+    <t>LP-049797</t>
+  </si>
+  <si>
+    <t>LP-049803</t>
+  </si>
+  <si>
+    <t>LP-049804</t>
+  </si>
+  <si>
+    <t>LP-049865</t>
+  </si>
+  <si>
+    <t>LP-049820</t>
+  </si>
+  <si>
+    <t>LP-049867</t>
+  </si>
+  <si>
+    <t>LP-049876</t>
+  </si>
+  <si>
+    <t>LP-049878</t>
+  </si>
+  <si>
+    <t>LP-049879</t>
+  </si>
+  <si>
+    <t>LP-049905</t>
+  </si>
+  <si>
+    <t>LP-049924</t>
+  </si>
+  <si>
+    <t>LP-049941</t>
+  </si>
+  <si>
+    <t>LP-050036</t>
   </si>
   <si>
     <t>LP-050063</t>
   </si>
   <si>
-    <t>LP-050076</t>
-  </si>
-  <si>
-    <t>LP-050677</t>
-  </si>
-  <si>
-    <t>LP-050078</t>
-  </si>
-  <si>
-    <t>LP-050079</t>
-  </si>
-  <si>
-    <t>LP-050080</t>
-  </si>
-  <si>
-    <t>LP-050178</t>
-  </si>
-  <si>
-    <t>LP-050201</t>
-  </si>
-  <si>
-    <t>LP-050321</t>
-  </si>
-  <si>
-    <t>LP-050495</t>
-  </si>
-  <si>
-    <t>LP-050497</t>
-  </si>
-  <si>
-    <t>LP-050499</t>
-  </si>
-  <si>
-    <t>LP-050543</t>
-  </si>
-  <si>
-    <t>LP-050638</t>
-  </si>
-  <si>
-    <t>LP-050641</t>
-  </si>
-  <si>
-    <t>LP-050703</t>
-  </si>
-  <si>
-    <t>LP-050807</t>
-  </si>
-  <si>
-    <t>LP-050808</t>
-  </si>
-  <si>
-    <t>LP-050809</t>
-  </si>
-  <si>
-    <t>LP-050810</t>
-  </si>
-  <si>
-    <t>LP-050811</t>
-  </si>
-  <si>
-    <t>LP-050812</t>
-  </si>
-  <si>
-    <t>LP-050846</t>
-  </si>
-  <si>
-    <t>LP-050885</t>
-  </si>
-  <si>
-    <t>LP-050919</t>
-  </si>
-  <si>
-    <t>LP-044259</t>
-  </si>
-  <si>
-    <t>LP-048461</t>
-  </si>
-  <si>
-    <t>LP-048588</t>
-  </si>
-  <si>
-    <t>LP-048657</t>
-  </si>
-  <si>
-    <t>LP-049087</t>
-  </si>
-  <si>
-    <t>LP-049409</t>
-  </si>
-  <si>
-    <t>LP-050081</t>
-  </si>
-  <si>
-    <t>LP-050250</t>
-  </si>
-  <si>
-    <t>LP-050588</t>
-  </si>
-  <si>
-    <t>LP-050704</t>
+    <t>LP-050111</t>
+  </si>
+  <si>
+    <t>LP-050121</t>
+  </si>
+  <si>
+    <t>LP-050122</t>
+  </si>
+  <si>
+    <t>LP-050149</t>
+  </si>
+  <si>
+    <t>LP-050165</t>
+  </si>
+  <si>
+    <t>LP-050214</t>
+  </si>
+  <si>
+    <t>LP-050215</t>
+  </si>
+  <si>
+    <t>LP-050218</t>
+  </si>
+  <si>
+    <t>LP-050219</t>
+  </si>
+  <si>
+    <t>LP-050220</t>
+  </si>
+  <si>
+    <t>LP-050223</t>
+  </si>
+  <si>
+    <t>LP-050225</t>
+  </si>
+  <si>
+    <t>LP-050240</t>
+  </si>
+  <si>
+    <t>LP-050287</t>
+  </si>
+  <si>
+    <t>LP-050293</t>
+  </si>
+  <si>
+    <t>LP-050294</t>
+  </si>
+  <si>
+    <t>LP-050326</t>
+  </si>
+  <si>
+    <t>LP-050327</t>
+  </si>
+  <si>
+    <t>LP-050335</t>
+  </si>
+  <si>
+    <t>LP-050336</t>
+  </si>
+  <si>
+    <t>LP-050352</t>
+  </si>
+  <si>
+    <t>LP-050368</t>
+  </si>
+  <si>
+    <t>LP-050473</t>
+  </si>
+  <si>
+    <t>LP-050500</t>
+  </si>
+  <si>
+    <t>LP-050507</t>
+  </si>
+  <si>
+    <t>LP-050530</t>
+  </si>
+  <si>
+    <t>LP-050531</t>
+  </si>
+  <si>
+    <t>LP-050534</t>
+  </si>
+  <si>
+    <t>LP-050556</t>
+  </si>
+  <si>
+    <t>LP-050557</t>
+  </si>
+  <si>
+    <t>LP-050562</t>
+  </si>
+  <si>
+    <t>LP-050580</t>
+  </si>
+  <si>
+    <t>LP-050596</t>
+  </si>
+  <si>
+    <t>LP-050618</t>
+  </si>
+  <si>
+    <t>LP-050700</t>
+  </si>
+  <si>
+    <t>LP-050702</t>
+  </si>
+  <si>
+    <t>LP-050727</t>
+  </si>
+  <si>
+    <t>LP-050799</t>
+  </si>
+  <si>
+    <t>LP-050800</t>
+  </si>
+  <si>
+    <t>LP-050876</t>
+  </si>
+  <si>
+    <t>LP-050881</t>
+  </si>
+  <si>
+    <t>LP-051058</t>
+  </si>
+  <si>
+    <t>LP-051104</t>
+  </si>
+  <si>
+    <t>LP-051106</t>
+  </si>
+  <si>
+    <t>LP-051188</t>
+  </si>
+  <si>
+    <t>LP-051194</t>
+  </si>
+  <si>
+    <t>LP-045689</t>
+  </si>
+  <si>
+    <t>LP-048446</t>
+  </si>
+  <si>
+    <t>LP-048460</t>
+  </si>
+  <si>
+    <t>LP-048469</t>
+  </si>
+  <si>
+    <t>LP-050587</t>
   </si>
 </sst>
 </file>
@@ -655,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A91"/>
+  <dimension ref="A1:A98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -668,17 +689,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -733,77 +754,77 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -883,237 +904,272 @@
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>80</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8ACC98-0763-49F2-A8A3-D7FE5D1DB96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E67205-B117-4D94-8F49-083C4993B5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,300 +20,249 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-041331</t>
-  </si>
-  <si>
-    <t>LP-045379</t>
-  </si>
-  <si>
-    <t>LP-046208</t>
-  </si>
-  <si>
-    <t>LP-046856</t>
-  </si>
-  <si>
-    <t>LP-046871</t>
-  </si>
-  <si>
-    <t>LP-047546</t>
-  </si>
-  <si>
-    <t>LP-047961</t>
-  </si>
-  <si>
-    <t>LP-047994</t>
-  </si>
-  <si>
-    <t>LP-048234</t>
-  </si>
-  <si>
-    <t>LP-048235</t>
-  </si>
-  <si>
-    <t>LP-048237</t>
-  </si>
-  <si>
-    <t>LP-048358</t>
-  </si>
-  <si>
-    <t>LP-048475</t>
-  </si>
-  <si>
-    <t>LP-048483</t>
-  </si>
-  <si>
-    <t>LP-048667</t>
-  </si>
-  <si>
-    <t>LP-048669</t>
-  </si>
-  <si>
-    <t>LP-048689</t>
-  </si>
-  <si>
-    <t>LP-048876</t>
-  </si>
-  <si>
-    <t>LP-048900</t>
-  </si>
-  <si>
-    <t>LP-048977</t>
-  </si>
-  <si>
-    <t>LP-049054</t>
-  </si>
-  <si>
-    <t>LP-049089</t>
-  </si>
-  <si>
-    <t>LP-049144</t>
-  </si>
-  <si>
-    <t>LP-049279</t>
-  </si>
-  <si>
-    <t>LP-049405</t>
-  </si>
-  <si>
-    <t>LP-049408</t>
-  </si>
-  <si>
-    <t>LP-049681</t>
-  </si>
-  <si>
-    <t>LP-049697</t>
-  </si>
-  <si>
-    <t>LP-049698</t>
-  </si>
-  <si>
-    <t>LP-049718</t>
-  </si>
-  <si>
-    <t>LP-049721</t>
-  </si>
-  <si>
-    <t>LP-049722</t>
-  </si>
-  <si>
-    <t>LP-049797</t>
-  </si>
-  <si>
-    <t>LP-049803</t>
-  </si>
-  <si>
-    <t>LP-049804</t>
-  </si>
-  <si>
-    <t>LP-049865</t>
-  </si>
-  <si>
-    <t>LP-049820</t>
-  </si>
-  <si>
-    <t>LP-049867</t>
-  </si>
-  <si>
-    <t>LP-049876</t>
-  </si>
-  <si>
-    <t>LP-049878</t>
-  </si>
-  <si>
-    <t>LP-049879</t>
-  </si>
-  <si>
-    <t>LP-049905</t>
-  </si>
-  <si>
-    <t>LP-049924</t>
-  </si>
-  <si>
-    <t>LP-049941</t>
-  </si>
-  <si>
-    <t>LP-050036</t>
-  </si>
-  <si>
-    <t>LP-050063</t>
-  </si>
-  <si>
-    <t>LP-050111</t>
-  </si>
-  <si>
-    <t>LP-050121</t>
-  </si>
-  <si>
-    <t>LP-050122</t>
-  </si>
-  <si>
-    <t>LP-050149</t>
-  </si>
-  <si>
-    <t>LP-050165</t>
-  </si>
-  <si>
-    <t>LP-050214</t>
-  </si>
-  <si>
-    <t>LP-050215</t>
-  </si>
-  <si>
-    <t>LP-050218</t>
-  </si>
-  <si>
-    <t>LP-050219</t>
-  </si>
-  <si>
-    <t>LP-050220</t>
-  </si>
-  <si>
-    <t>LP-050223</t>
-  </si>
-  <si>
-    <t>LP-050225</t>
-  </si>
-  <si>
-    <t>LP-050240</t>
-  </si>
-  <si>
-    <t>LP-050287</t>
-  </si>
-  <si>
-    <t>LP-050293</t>
-  </si>
-  <si>
-    <t>LP-050294</t>
-  </si>
-  <si>
-    <t>LP-050326</t>
-  </si>
-  <si>
-    <t>LP-050327</t>
-  </si>
-  <si>
-    <t>LP-050335</t>
-  </si>
-  <si>
-    <t>LP-050336</t>
-  </si>
-  <si>
-    <t>LP-050352</t>
-  </si>
-  <si>
-    <t>LP-050368</t>
-  </si>
-  <si>
-    <t>LP-050473</t>
-  </si>
-  <si>
-    <t>LP-050500</t>
-  </si>
-  <si>
-    <t>LP-050507</t>
-  </si>
-  <si>
-    <t>LP-050530</t>
-  </si>
-  <si>
-    <t>LP-050531</t>
-  </si>
-  <si>
-    <t>LP-050534</t>
-  </si>
-  <si>
-    <t>LP-050556</t>
-  </si>
-  <si>
-    <t>LP-050557</t>
-  </si>
-  <si>
-    <t>LP-050562</t>
-  </si>
-  <si>
-    <t>LP-050580</t>
-  </si>
-  <si>
-    <t>LP-050596</t>
-  </si>
-  <si>
-    <t>LP-050618</t>
-  </si>
-  <si>
-    <t>LP-050700</t>
-  </si>
-  <si>
-    <t>LP-050702</t>
-  </si>
-  <si>
-    <t>LP-050727</t>
-  </si>
-  <si>
-    <t>LP-050799</t>
-  </si>
-  <si>
-    <t>LP-050800</t>
-  </si>
-  <si>
-    <t>LP-050876</t>
-  </si>
-  <si>
-    <t>LP-050881</t>
-  </si>
-  <si>
-    <t>LP-051058</t>
-  </si>
-  <si>
-    <t>LP-051104</t>
-  </si>
-  <si>
-    <t>LP-051106</t>
-  </si>
-  <si>
-    <t>LP-051188</t>
-  </si>
-  <si>
-    <t>LP-051194</t>
-  </si>
-  <si>
-    <t>LP-045689</t>
-  </si>
-  <si>
-    <t>LP-048446</t>
-  </si>
-  <si>
-    <t>LP-048460</t>
-  </si>
-  <si>
-    <t>LP-048469</t>
-  </si>
-  <si>
-    <t>LP-050587</t>
+    <t>LP-033372</t>
+  </si>
+  <si>
+    <t>LP-044444</t>
+  </si>
+  <si>
+    <t>LP-046043</t>
+  </si>
+  <si>
+    <t>LP-046044</t>
+  </si>
+  <si>
+    <t>LP-046692</t>
+  </si>
+  <si>
+    <t>LP-047416</t>
+  </si>
+  <si>
+    <t>LP-047460</t>
+  </si>
+  <si>
+    <t>LP-047461</t>
+  </si>
+  <si>
+    <t>LP-047462</t>
+  </si>
+  <si>
+    <t>LP-047463</t>
+  </si>
+  <si>
+    <t>LP-047766</t>
+  </si>
+  <si>
+    <t>LP-047954</t>
+  </si>
+  <si>
+    <t>LP-048009</t>
+  </si>
+  <si>
+    <t>LP-048020</t>
+  </si>
+  <si>
+    <t>LP-048099</t>
+  </si>
+  <si>
+    <t>LP-048355</t>
+  </si>
+  <si>
+    <t>LP-048356</t>
+  </si>
+  <si>
+    <t>LP-048468</t>
+  </si>
+  <si>
+    <t>LP-048474</t>
+  </si>
+  <si>
+    <t>LP-048851</t>
+  </si>
+  <si>
+    <t>LP-049053</t>
+  </si>
+  <si>
+    <t>LP-049067</t>
+  </si>
+  <si>
+    <t>LP-049104</t>
+  </si>
+  <si>
+    <t>LP-049303</t>
+  </si>
+  <si>
+    <t>LP-049403</t>
+  </si>
+  <si>
+    <t>LP-049412</t>
+  </si>
+  <si>
+    <t>LP-049429</t>
+  </si>
+  <si>
+    <t>LP-049430</t>
+  </si>
+  <si>
+    <t>LP-049655</t>
+  </si>
+  <si>
+    <t>LP-049716</t>
+  </si>
+  <si>
+    <t>LP-049783</t>
+  </si>
+  <si>
+    <t>LP-049784</t>
+  </si>
+  <si>
+    <t>LP-049809</t>
+  </si>
+  <si>
+    <t>LP-049923</t>
+  </si>
+  <si>
+    <t>LP-050006</t>
+  </si>
+  <si>
+    <t>LP-050008</t>
+  </si>
+  <si>
+    <t>LP-050014</t>
+  </si>
+  <si>
+    <t>LP-050052</t>
+  </si>
+  <si>
+    <t>LP-050073</t>
+  </si>
+  <si>
+    <t>LP-050110</t>
+  </si>
+  <si>
+    <t>LP-050164</t>
+  </si>
+  <si>
+    <t>LP-050207</t>
+  </si>
+  <si>
+    <t>LP-050290</t>
+  </si>
+  <si>
+    <t>LP-050297</t>
+  </si>
+  <si>
+    <t>LP-050315</t>
+  </si>
+  <si>
+    <t>LP-050332</t>
+  </si>
+  <si>
+    <t>LP-050342</t>
+  </si>
+  <si>
+    <t>LP-050338</t>
+  </si>
+  <si>
+    <t>LP-050358</t>
+  </si>
+  <si>
+    <t>LP-050374</t>
+  </si>
+  <si>
+    <t>LP-050483</t>
+  </si>
+  <si>
+    <t>LP-050490</t>
+  </si>
+  <si>
+    <t>LP-050502</t>
+  </si>
+  <si>
+    <t>LP-050541</t>
+  </si>
+  <si>
+    <t>LP-050555</t>
+  </si>
+  <si>
+    <t>LP-050611</t>
+  </si>
+  <si>
+    <t>LP-050619</t>
+  </si>
+  <si>
+    <t>LP-050625</t>
+  </si>
+  <si>
+    <t>LP-050637</t>
+  </si>
+  <si>
+    <t>LP-050698</t>
+  </si>
+  <si>
+    <t>LP-050728</t>
+  </si>
+  <si>
+    <t>LP-050838</t>
+  </si>
+  <si>
+    <t>LP-050841</t>
+  </si>
+  <si>
+    <t>LP-050884</t>
+  </si>
+  <si>
+    <t>LP-050398</t>
+  </si>
+  <si>
+    <t>LP-050940</t>
+  </si>
+  <si>
+    <t>LP-051005</t>
+  </si>
+  <si>
+    <t>LP-051124</t>
+  </si>
+  <si>
+    <t>LP-051125</t>
+  </si>
+  <si>
+    <t>LP-051211</t>
+  </si>
+  <si>
+    <t>LP-051247</t>
+  </si>
+  <si>
+    <t>LP-048353</t>
+  </si>
+  <si>
+    <t>LP-048699</t>
+  </si>
+  <si>
+    <t>LP-049483</t>
+  </si>
+  <si>
+    <t>LP-049983</t>
+  </si>
+  <si>
+    <t>LP-050594</t>
+  </si>
+  <si>
+    <t>LP-050636</t>
+  </si>
+  <si>
+    <t>LP-050694</t>
+  </si>
+  <si>
+    <t>LP-050705</t>
+  </si>
+  <si>
+    <t>LP-050897</t>
   </si>
 </sst>
 </file>
@@ -676,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A98"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -699,182 +648,182 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
@@ -984,192 +933,107 @@
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E67205-B117-4D94-8F49-083C4993B5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A618D29-6345-46D7-A695-D414A7636C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,249 +20,264 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-033372</t>
-  </si>
-  <si>
-    <t>LP-044444</t>
-  </si>
-  <si>
-    <t>LP-046043</t>
-  </si>
-  <si>
-    <t>LP-046044</t>
-  </si>
-  <si>
-    <t>LP-046692</t>
-  </si>
-  <si>
-    <t>LP-047416</t>
-  </si>
-  <si>
-    <t>LP-047460</t>
-  </si>
-  <si>
-    <t>LP-047461</t>
-  </si>
-  <si>
-    <t>LP-047462</t>
-  </si>
-  <si>
-    <t>LP-047463</t>
-  </si>
-  <si>
-    <t>LP-047766</t>
-  </si>
-  <si>
-    <t>LP-047954</t>
-  </si>
-  <si>
-    <t>LP-048009</t>
-  </si>
-  <si>
-    <t>LP-048020</t>
-  </si>
-  <si>
-    <t>LP-048099</t>
-  </si>
-  <si>
-    <t>LP-048355</t>
-  </si>
-  <si>
-    <t>LP-048356</t>
-  </si>
-  <si>
-    <t>LP-048468</t>
-  </si>
-  <si>
-    <t>LP-048474</t>
-  </si>
-  <si>
-    <t>LP-048851</t>
-  </si>
-  <si>
-    <t>LP-049053</t>
-  </si>
-  <si>
-    <t>LP-049067</t>
-  </si>
-  <si>
-    <t>LP-049104</t>
-  </si>
-  <si>
-    <t>LP-049303</t>
-  </si>
-  <si>
-    <t>LP-049403</t>
-  </si>
-  <si>
-    <t>LP-049412</t>
-  </si>
-  <si>
-    <t>LP-049429</t>
-  </si>
-  <si>
-    <t>LP-049430</t>
-  </si>
-  <si>
-    <t>LP-049655</t>
-  </si>
-  <si>
-    <t>LP-049716</t>
-  </si>
-  <si>
-    <t>LP-049783</t>
-  </si>
-  <si>
-    <t>LP-049784</t>
-  </si>
-  <si>
-    <t>LP-049809</t>
-  </si>
-  <si>
-    <t>LP-049923</t>
-  </si>
-  <si>
-    <t>LP-050006</t>
-  </si>
-  <si>
-    <t>LP-050008</t>
-  </si>
-  <si>
-    <t>LP-050014</t>
-  </si>
-  <si>
-    <t>LP-050052</t>
-  </si>
-  <si>
-    <t>LP-050073</t>
-  </si>
-  <si>
-    <t>LP-050110</t>
-  </si>
-  <si>
-    <t>LP-050164</t>
-  </si>
-  <si>
-    <t>LP-050207</t>
-  </si>
-  <si>
-    <t>LP-050290</t>
-  </si>
-  <si>
-    <t>LP-050297</t>
-  </si>
-  <si>
-    <t>LP-050315</t>
-  </si>
-  <si>
-    <t>LP-050332</t>
-  </si>
-  <si>
-    <t>LP-050342</t>
-  </si>
-  <si>
-    <t>LP-050338</t>
-  </si>
-  <si>
-    <t>LP-050358</t>
-  </si>
-  <si>
-    <t>LP-050374</t>
-  </si>
-  <si>
-    <t>LP-050483</t>
-  </si>
-  <si>
-    <t>LP-050490</t>
-  </si>
-  <si>
-    <t>LP-050502</t>
-  </si>
-  <si>
-    <t>LP-050541</t>
-  </si>
-  <si>
-    <t>LP-050555</t>
-  </si>
-  <si>
-    <t>LP-050611</t>
-  </si>
-  <si>
-    <t>LP-050619</t>
-  </si>
-  <si>
-    <t>LP-050625</t>
-  </si>
-  <si>
-    <t>LP-050637</t>
-  </si>
-  <si>
-    <t>LP-050698</t>
-  </si>
-  <si>
-    <t>LP-050728</t>
-  </si>
-  <si>
-    <t>LP-050838</t>
-  </si>
-  <si>
-    <t>LP-050841</t>
-  </si>
-  <si>
-    <t>LP-050884</t>
-  </si>
-  <si>
-    <t>LP-050398</t>
-  </si>
-  <si>
-    <t>LP-050940</t>
-  </si>
-  <si>
-    <t>LP-051005</t>
-  </si>
-  <si>
-    <t>LP-051124</t>
-  </si>
-  <si>
-    <t>LP-051125</t>
-  </si>
-  <si>
-    <t>LP-051211</t>
-  </si>
-  <si>
-    <t>LP-051247</t>
-  </si>
-  <si>
-    <t>LP-048353</t>
-  </si>
-  <si>
-    <t>LP-048699</t>
-  </si>
-  <si>
-    <t>LP-049483</t>
-  </si>
-  <si>
-    <t>LP-049983</t>
-  </si>
-  <si>
-    <t>LP-050594</t>
-  </si>
-  <si>
-    <t>LP-050636</t>
-  </si>
-  <si>
-    <t>LP-050694</t>
-  </si>
-  <si>
-    <t>LP-050705</t>
-  </si>
-  <si>
-    <t>LP-050897</t>
+    <t>LP-043816</t>
+  </si>
+  <si>
+    <t>LP-045946</t>
+  </si>
+  <si>
+    <t>LP-046294</t>
+  </si>
+  <si>
+    <t>LP-046869</t>
+  </si>
+  <si>
+    <t>LP-046870</t>
+  </si>
+  <si>
+    <t>LP-047083</t>
+  </si>
+  <si>
+    <t>LP-047208</t>
+  </si>
+  <si>
+    <t>LP-047290</t>
+  </si>
+  <si>
+    <t>LP-047458</t>
+  </si>
+  <si>
+    <t>LP-047466</t>
+  </si>
+  <si>
+    <t>LP-047763</t>
+  </si>
+  <si>
+    <t>LP-047769</t>
+  </si>
+  <si>
+    <t>LP-047852</t>
+  </si>
+  <si>
+    <t>LP-047968</t>
+  </si>
+  <si>
+    <t>LP-048006</t>
+  </si>
+  <si>
+    <t>LP-048320</t>
+  </si>
+  <si>
+    <t>LP-048467</t>
+  </si>
+  <si>
+    <t>LP-048664</t>
+  </si>
+  <si>
+    <t>LP-048666</t>
+  </si>
+  <si>
+    <t>LP-048700</t>
+  </si>
+  <si>
+    <t>LP-048910</t>
+  </si>
+  <si>
+    <t>LP-048912</t>
+  </si>
+  <si>
+    <t>LP-048913</t>
+  </si>
+  <si>
+    <t>LP-048914</t>
+  </si>
+  <si>
+    <t>LP-049023</t>
+  </si>
+  <si>
+    <t>LP-049081</t>
+  </si>
+  <si>
+    <t>LP-049366</t>
+  </si>
+  <si>
+    <t>LP-049438</t>
+  </si>
+  <si>
+    <t>LP-049827</t>
+  </si>
+  <si>
+    <t>LP-049982</t>
+  </si>
+  <si>
+    <t>LP-049984</t>
+  </si>
+  <si>
+    <t>LP-049985</t>
+  </si>
+  <si>
+    <t>LP-050017</t>
+  </si>
+  <si>
+    <t>LP-050108</t>
+  </si>
+  <si>
+    <t>LP-050109</t>
+  </si>
+  <si>
+    <t>LP-050226</t>
+  </si>
+  <si>
+    <t>LP-050239</t>
+  </si>
+  <si>
+    <t>LP-050264</t>
+  </si>
+  <si>
+    <t>LP-050318</t>
+  </si>
+  <si>
+    <t>LP-050355</t>
+  </si>
+  <si>
+    <t>LP-050371</t>
+  </si>
+  <si>
+    <t>LP-050372</t>
+  </si>
+  <si>
+    <t>LP-050413</t>
+  </si>
+  <si>
+    <t>LP-050434</t>
+  </si>
+  <si>
+    <t>LP-050485</t>
+  </si>
+  <si>
+    <t>LP-050493</t>
+  </si>
+  <si>
+    <t>LP-050496</t>
+  </si>
+  <si>
+    <t>LP-050572</t>
+  </si>
+  <si>
+    <t>LP-050573</t>
+  </si>
+  <si>
+    <t>LP-050584</t>
+  </si>
+  <si>
+    <t>LP-050597</t>
+  </si>
+  <si>
+    <t>LP-050634</t>
+  </si>
+  <si>
+    <t>LP-050659</t>
+  </si>
+  <si>
+    <t>LP-050691</t>
+  </si>
+  <si>
+    <t>LP-050692</t>
+  </si>
+  <si>
+    <t>LP-050701</t>
+  </si>
+  <si>
+    <t>LP-050725</t>
+  </si>
+  <si>
+    <t>LP-050831</t>
+  </si>
+  <si>
+    <t>LP-050832</t>
+  </si>
+  <si>
+    <t>LP-050833</t>
+  </si>
+  <si>
+    <t>LP-050879</t>
+  </si>
+  <si>
+    <t>LP-050880</t>
+  </si>
+  <si>
+    <t>LP-050908</t>
+  </si>
+  <si>
+    <t>LP-050914</t>
+  </si>
+  <si>
+    <t>LP-050953</t>
+  </si>
+  <si>
+    <t>LP-050955</t>
+  </si>
+  <si>
+    <t>LP-051131</t>
+  </si>
+  <si>
+    <t>LP-051185</t>
+  </si>
+  <si>
+    <t>LP-051268</t>
+  </si>
+  <si>
+    <t>LP-051550</t>
+  </si>
+  <si>
+    <t>LP-047455</t>
+  </si>
+  <si>
+    <t>LP-047762</t>
+  </si>
+  <si>
+    <t>LP-047928</t>
+  </si>
+  <si>
+    <t>LP-048471</t>
+  </si>
+  <si>
+    <t>LP-048473</t>
+  </si>
+  <si>
+    <t>LP-048579</t>
+  </si>
+  <si>
+    <t>LP-048598</t>
+  </si>
+  <si>
+    <t>LP-048599</t>
+  </si>
+  <si>
+    <t>LP-048600</t>
+  </si>
+  <si>
+    <t>LP-048601</t>
+  </si>
+  <si>
+    <t>LP-048603</t>
+  </si>
+  <si>
+    <t>LP-048605</t>
+  </si>
+  <si>
+    <t>LP-048606</t>
+  </si>
+  <si>
+    <t>LP-048909</t>
+  </si>
+  <si>
+    <t>LP-049497</t>
   </si>
 </sst>
 </file>
@@ -625,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A81"/>
+  <dimension ref="A1:A86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -678,362 +693,387 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A618D29-6345-46D7-A695-D414A7636C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F617FAD-F029-4382-BE7D-8FE9C23AF56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,264 +20,171 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-043816</t>
-  </si>
-  <si>
-    <t>LP-045946</t>
-  </si>
-  <si>
-    <t>LP-046294</t>
-  </si>
-  <si>
-    <t>LP-046869</t>
-  </si>
-  <si>
-    <t>LP-046870</t>
-  </si>
-  <si>
-    <t>LP-047083</t>
-  </si>
-  <si>
-    <t>LP-047208</t>
-  </si>
-  <si>
-    <t>LP-047290</t>
-  </si>
-  <si>
-    <t>LP-047458</t>
-  </si>
-  <si>
-    <t>LP-047466</t>
-  </si>
-  <si>
-    <t>LP-047763</t>
-  </si>
-  <si>
-    <t>LP-047769</t>
-  </si>
-  <si>
-    <t>LP-047852</t>
-  </si>
-  <si>
-    <t>LP-047968</t>
-  </si>
-  <si>
-    <t>LP-048006</t>
-  </si>
-  <si>
-    <t>LP-048320</t>
-  </si>
-  <si>
-    <t>LP-048467</t>
-  </si>
-  <si>
-    <t>LP-048664</t>
-  </si>
-  <si>
-    <t>LP-048666</t>
-  </si>
-  <si>
-    <t>LP-048700</t>
-  </si>
-  <si>
-    <t>LP-048910</t>
-  </si>
-  <si>
-    <t>LP-048912</t>
-  </si>
-  <si>
-    <t>LP-048913</t>
-  </si>
-  <si>
-    <t>LP-048914</t>
-  </si>
-  <si>
-    <t>LP-049023</t>
-  </si>
-  <si>
-    <t>LP-049081</t>
-  </si>
-  <si>
-    <t>LP-049366</t>
-  </si>
-  <si>
-    <t>LP-049438</t>
-  </si>
-  <si>
-    <t>LP-049827</t>
-  </si>
-  <si>
-    <t>LP-049982</t>
-  </si>
-  <si>
-    <t>LP-049984</t>
-  </si>
-  <si>
-    <t>LP-049985</t>
-  </si>
-  <si>
-    <t>LP-050017</t>
-  </si>
-  <si>
-    <t>LP-050108</t>
-  </si>
-  <si>
-    <t>LP-050109</t>
-  </si>
-  <si>
-    <t>LP-050226</t>
-  </si>
-  <si>
-    <t>LP-050239</t>
-  </si>
-  <si>
-    <t>LP-050264</t>
-  </si>
-  <si>
-    <t>LP-050318</t>
-  </si>
-  <si>
-    <t>LP-050355</t>
-  </si>
-  <si>
-    <t>LP-050371</t>
-  </si>
-  <si>
-    <t>LP-050372</t>
-  </si>
-  <si>
-    <t>LP-050413</t>
-  </si>
-  <si>
-    <t>LP-050434</t>
-  </si>
-  <si>
-    <t>LP-050485</t>
-  </si>
-  <si>
-    <t>LP-050493</t>
-  </si>
-  <si>
-    <t>LP-050496</t>
-  </si>
-  <si>
-    <t>LP-050572</t>
-  </si>
-  <si>
-    <t>LP-050573</t>
-  </si>
-  <si>
-    <t>LP-050584</t>
-  </si>
-  <si>
-    <t>LP-050597</t>
-  </si>
-  <si>
-    <t>LP-050634</t>
-  </si>
-  <si>
-    <t>LP-050659</t>
-  </si>
-  <si>
-    <t>LP-050691</t>
-  </si>
-  <si>
-    <t>LP-050692</t>
-  </si>
-  <si>
-    <t>LP-050701</t>
-  </si>
-  <si>
-    <t>LP-050725</t>
-  </si>
-  <si>
-    <t>LP-050831</t>
-  </si>
-  <si>
-    <t>LP-050832</t>
-  </si>
-  <si>
-    <t>LP-050833</t>
-  </si>
-  <si>
-    <t>LP-050879</t>
-  </si>
-  <si>
-    <t>LP-050880</t>
-  </si>
-  <si>
-    <t>LP-050908</t>
-  </si>
-  <si>
-    <t>LP-050914</t>
-  </si>
-  <si>
-    <t>LP-050953</t>
-  </si>
-  <si>
-    <t>LP-050955</t>
-  </si>
-  <si>
-    <t>LP-051131</t>
-  </si>
-  <si>
-    <t>LP-051185</t>
-  </si>
-  <si>
-    <t>LP-051268</t>
-  </si>
-  <si>
-    <t>LP-051550</t>
-  </si>
-  <si>
-    <t>LP-047455</t>
-  </si>
-  <si>
-    <t>LP-047762</t>
-  </si>
-  <si>
-    <t>LP-047928</t>
-  </si>
-  <si>
-    <t>LP-048471</t>
-  </si>
-  <si>
-    <t>LP-048473</t>
-  </si>
-  <si>
-    <t>LP-048579</t>
-  </si>
-  <si>
-    <t>LP-048598</t>
-  </si>
-  <si>
-    <t>LP-048599</t>
-  </si>
-  <si>
-    <t>LP-048600</t>
-  </si>
-  <si>
-    <t>LP-048601</t>
-  </si>
-  <si>
-    <t>LP-048603</t>
-  </si>
-  <si>
-    <t>LP-048605</t>
-  </si>
-  <si>
-    <t>LP-048606</t>
-  </si>
-  <si>
-    <t>LP-048909</t>
-  </si>
-  <si>
-    <t>LP-049497</t>
+    <t>LP-044555</t>
+  </si>
+  <si>
+    <t>LP-044804</t>
+  </si>
+  <si>
+    <t>LP-046037</t>
+  </si>
+  <si>
+    <t>LP-047277</t>
+  </si>
+  <si>
+    <t>LP-047286</t>
+  </si>
+  <si>
+    <t>LP-047620</t>
+  </si>
+  <si>
+    <t>LP-047709</t>
+  </si>
+  <si>
+    <t>LP-047955</t>
+  </si>
+  <si>
+    <t>LP-047964</t>
+  </si>
+  <si>
+    <t>LP-047970</t>
+  </si>
+  <si>
+    <t>LP-048026</t>
+  </si>
+  <si>
+    <t>LP-048350</t>
+  </si>
+  <si>
+    <t>LP-048383</t>
+  </si>
+  <si>
+    <t>LP-048427</t>
+  </si>
+  <si>
+    <t>LP-048580</t>
+  </si>
+  <si>
+    <t>LP-048640</t>
+  </si>
+  <si>
+    <t>LP-048641</t>
+  </si>
+  <si>
+    <t>LP-049056</t>
+  </si>
+  <si>
+    <t>LP-049092</t>
+  </si>
+  <si>
+    <t>LP-049482</t>
+  </si>
+  <si>
+    <t>LP-049513</t>
+  </si>
+  <si>
+    <t>LP-049657</t>
+  </si>
+  <si>
+    <t>LP-049714</t>
+  </si>
+  <si>
+    <t>LP-049716</t>
+  </si>
+  <si>
+    <t>LP-049888</t>
+  </si>
+  <si>
+    <t>LP-050010</t>
+  </si>
+  <si>
+    <t>LP-050262</t>
+  </si>
+  <si>
+    <t>LP-050341</t>
+  </si>
+  <si>
+    <t>LP-050487</t>
+  </si>
+  <si>
+    <t>LP-050503</t>
+  </si>
+  <si>
+    <t>LP-050609</t>
+  </si>
+  <si>
+    <t>LP-050612</t>
+  </si>
+  <si>
+    <t>LP-050693</t>
+  </si>
+  <si>
+    <t>LP-050695</t>
+  </si>
+  <si>
+    <t>LP-050696</t>
+  </si>
+  <si>
+    <t>LP-050826</t>
+  </si>
+  <si>
+    <t>LP-050888</t>
+  </si>
+  <si>
+    <t>LP-050992</t>
+  </si>
+  <si>
+    <t>LP-051003</t>
+  </si>
+  <si>
+    <t>LP-051109</t>
+  </si>
+  <si>
+    <t>LP-051197</t>
+  </si>
+  <si>
+    <t>LP-051242</t>
+  </si>
+  <si>
+    <t>LP-051290</t>
+  </si>
+  <si>
+    <t>LP-051292</t>
+  </si>
+  <si>
+    <t>LP-051371</t>
+  </si>
+  <si>
+    <t>LP-051464</t>
+  </si>
+  <si>
+    <t>LP-051480</t>
+  </si>
+  <si>
+    <t>LP-047987</t>
+  </si>
+  <si>
+    <t>LP-048441</t>
+  </si>
+  <si>
+    <t>LP-048472</t>
+  </si>
+  <si>
+    <t>LP-050337</t>
+  </si>
+  <si>
+    <t>LP-050585</t>
+  </si>
+  <si>
+    <t>LP-050743</t>
+  </si>
+  <si>
+    <t>LP-051200</t>
   </si>
 </sst>
 </file>
@@ -640,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A86"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -693,12 +600,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -708,32 +615,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -753,327 +660,182 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F617FAD-F029-4382-BE7D-8FE9C23AF56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06936724-92C5-45B1-B9C7-6E2220ED7651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,171 +20,198 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-044555</t>
-  </si>
-  <si>
-    <t>LP-044804</t>
-  </si>
-  <si>
-    <t>LP-046037</t>
-  </si>
-  <si>
-    <t>LP-047277</t>
-  </si>
-  <si>
-    <t>LP-047286</t>
-  </si>
-  <si>
-    <t>LP-047620</t>
-  </si>
-  <si>
-    <t>LP-047709</t>
-  </si>
-  <si>
-    <t>LP-047955</t>
-  </si>
-  <si>
-    <t>LP-047964</t>
-  </si>
-  <si>
-    <t>LP-047970</t>
-  </si>
-  <si>
-    <t>LP-048026</t>
-  </si>
-  <si>
-    <t>LP-048350</t>
-  </si>
-  <si>
-    <t>LP-048383</t>
-  </si>
-  <si>
-    <t>LP-048427</t>
-  </si>
-  <si>
-    <t>LP-048580</t>
-  </si>
-  <si>
-    <t>LP-048640</t>
-  </si>
-  <si>
-    <t>LP-048641</t>
-  </si>
-  <si>
-    <t>LP-049056</t>
-  </si>
-  <si>
-    <t>LP-049092</t>
-  </si>
-  <si>
-    <t>LP-049482</t>
-  </si>
-  <si>
-    <t>LP-049513</t>
-  </si>
-  <si>
-    <t>LP-049657</t>
-  </si>
-  <si>
-    <t>LP-049714</t>
-  </si>
-  <si>
-    <t>LP-049716</t>
-  </si>
-  <si>
-    <t>LP-049888</t>
-  </si>
-  <si>
-    <t>LP-050010</t>
-  </si>
-  <si>
-    <t>LP-050262</t>
-  </si>
-  <si>
-    <t>LP-050341</t>
-  </si>
-  <si>
-    <t>LP-050487</t>
-  </si>
-  <si>
-    <t>LP-050503</t>
-  </si>
-  <si>
-    <t>LP-050609</t>
-  </si>
-  <si>
-    <t>LP-050612</t>
-  </si>
-  <si>
-    <t>LP-050693</t>
-  </si>
-  <si>
-    <t>LP-050695</t>
-  </si>
-  <si>
-    <t>LP-050696</t>
-  </si>
-  <si>
-    <t>LP-050826</t>
-  </si>
-  <si>
-    <t>LP-050888</t>
-  </si>
-  <si>
-    <t>LP-050992</t>
-  </si>
-  <si>
-    <t>LP-051003</t>
-  </si>
-  <si>
-    <t>LP-051109</t>
-  </si>
-  <si>
-    <t>LP-051197</t>
-  </si>
-  <si>
-    <t>LP-051242</t>
-  </si>
-  <si>
-    <t>LP-051290</t>
-  </si>
-  <si>
-    <t>LP-051292</t>
-  </si>
-  <si>
-    <t>LP-051371</t>
-  </si>
-  <si>
-    <t>LP-051464</t>
-  </si>
-  <si>
-    <t>LP-051480</t>
-  </si>
-  <si>
-    <t>LP-047987</t>
-  </si>
-  <si>
-    <t>LP-048441</t>
-  </si>
-  <si>
-    <t>LP-048472</t>
-  </si>
-  <si>
-    <t>LP-050337</t>
-  </si>
-  <si>
-    <t>LP-050585</t>
-  </si>
-  <si>
-    <t>LP-050743</t>
-  </si>
-  <si>
-    <t>LP-051200</t>
+    <t>LP-033510</t>
+  </si>
+  <si>
+    <t>LP-033548</t>
+  </si>
+  <si>
+    <t>LP-042267</t>
+  </si>
+  <si>
+    <t>LP-047420</t>
+  </si>
+  <si>
+    <t>LP-047986</t>
+  </si>
+  <si>
+    <t>LP-048001</t>
+  </si>
+  <si>
+    <t>LP-048002</t>
+  </si>
+  <si>
+    <t>LP-048178</t>
+  </si>
+  <si>
+    <t>LP-048638</t>
+  </si>
+  <si>
+    <t>LP-048663</t>
+  </si>
+  <si>
+    <t>LP-048718</t>
+  </si>
+  <si>
+    <t>LP-049234</t>
+  </si>
+  <si>
+    <t>LP-049371</t>
+  </si>
+  <si>
+    <t>LP-049551</t>
+  </si>
+  <si>
+    <t>LP-049678</t>
+  </si>
+  <si>
+    <t>LP-050030</t>
+  </si>
+  <si>
+    <t>LP-050126</t>
+  </si>
+  <si>
+    <t>LP-050146</t>
+  </si>
+  <si>
+    <t>LP-050150</t>
+  </si>
+  <si>
+    <t>LP-650151</t>
+  </si>
+  <si>
+    <t>LP-050200</t>
+  </si>
+  <si>
+    <t>LP-050272</t>
+  </si>
+  <si>
+    <t>LP-050313</t>
+  </si>
+  <si>
+    <t>LP-050359</t>
+  </si>
+  <si>
+    <t>LP-050418</t>
+  </si>
+  <si>
+    <t>LP-050424</t>
+  </si>
+  <si>
+    <t>LP-050452</t>
+  </si>
+  <si>
+    <t>LP-050494</t>
+  </si>
+  <si>
+    <t>LP-050498</t>
+  </si>
+  <si>
+    <t>LP-050571</t>
+  </si>
+  <si>
+    <t>LP-050598</t>
+  </si>
+  <si>
+    <t>LP-050685</t>
+  </si>
+  <si>
+    <t>LP-050697</t>
+  </si>
+  <si>
+    <t>LP-050325</t>
+  </si>
+  <si>
+    <t>LP-050836</t>
+  </si>
+  <si>
+    <t>LP-050844</t>
+  </si>
+  <si>
+    <t>LP-050926</t>
+  </si>
+  <si>
+    <t>LP-050961</t>
+  </si>
+  <si>
+    <t>LP-050962</t>
+  </si>
+  <si>
+    <t>LP-050993</t>
+  </si>
+  <si>
+    <t>LP-050994</t>
+  </si>
+  <si>
+    <t>LP-050995</t>
+  </si>
+  <si>
+    <t>LP-050996</t>
+  </si>
+  <si>
+    <t>LP-050997</t>
+  </si>
+  <si>
+    <t>LP-050998</t>
+  </si>
+  <si>
+    <t>LP-050999</t>
+  </si>
+  <si>
+    <t>LP-051026</t>
+  </si>
+  <si>
+    <t>LP-051105</t>
+  </si>
+  <si>
+    <t>LP-051107</t>
+  </si>
+  <si>
+    <t>LP-051119</t>
+  </si>
+  <si>
+    <t>LP-051128</t>
+  </si>
+  <si>
+    <t>LP-051129</t>
+  </si>
+  <si>
+    <t>LP-051251</t>
+  </si>
+  <si>
+    <t>LP-051259</t>
+  </si>
+  <si>
+    <t>LP-051350</t>
+  </si>
+  <si>
+    <t>LP-051453</t>
+  </si>
+  <si>
+    <t>LP-051500</t>
+  </si>
+  <si>
+    <t>LP-051537</t>
+  </si>
+  <si>
+    <t>LP-048392</t>
+  </si>
+  <si>
+    <t>LP-050347</t>
+  </si>
+  <si>
+    <t>LP-050370</t>
+  </si>
+  <si>
+    <t>LP-050599</t>
+  </si>
+  <si>
+    <t>LP-050982</t>
   </si>
 </sst>
 </file>
@@ -547,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -600,12 +627,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -635,207 +662,242 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06936724-92C5-45B1-B9C7-6E2220ED7651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0844059-5FF2-40C7-8BD1-A311CD41F948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,198 +20,138 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-033510</t>
-  </si>
-  <si>
-    <t>LP-033548</t>
-  </si>
-  <si>
-    <t>LP-042267</t>
-  </si>
-  <si>
-    <t>LP-047420</t>
-  </si>
-  <si>
-    <t>LP-047986</t>
-  </si>
-  <si>
-    <t>LP-048001</t>
-  </si>
-  <si>
-    <t>LP-048002</t>
-  </si>
-  <si>
-    <t>LP-048178</t>
-  </si>
-  <si>
-    <t>LP-048638</t>
-  </si>
-  <si>
-    <t>LP-048663</t>
-  </si>
-  <si>
-    <t>LP-048718</t>
-  </si>
-  <si>
-    <t>LP-049234</t>
-  </si>
-  <si>
-    <t>LP-049371</t>
-  </si>
-  <si>
-    <t>LP-049551</t>
-  </si>
-  <si>
-    <t>LP-049678</t>
-  </si>
-  <si>
-    <t>LP-050030</t>
-  </si>
-  <si>
-    <t>LP-050126</t>
-  </si>
-  <si>
-    <t>LP-050146</t>
-  </si>
-  <si>
-    <t>LP-050150</t>
-  </si>
-  <si>
-    <t>LP-650151</t>
-  </si>
-  <si>
-    <t>LP-050200</t>
-  </si>
-  <si>
-    <t>LP-050272</t>
-  </si>
-  <si>
-    <t>LP-050313</t>
-  </si>
-  <si>
-    <t>LP-050359</t>
-  </si>
-  <si>
-    <t>LP-050418</t>
-  </si>
-  <si>
-    <t>LP-050424</t>
-  </si>
-  <si>
-    <t>LP-050452</t>
-  </si>
-  <si>
-    <t>LP-050494</t>
-  </si>
-  <si>
-    <t>LP-050498</t>
-  </si>
-  <si>
-    <t>LP-050571</t>
-  </si>
-  <si>
-    <t>LP-050598</t>
-  </si>
-  <si>
-    <t>LP-050685</t>
-  </si>
-  <si>
-    <t>LP-050697</t>
-  </si>
-  <si>
-    <t>LP-050325</t>
-  </si>
-  <si>
-    <t>LP-050836</t>
-  </si>
-  <si>
-    <t>LP-050844</t>
-  </si>
-  <si>
-    <t>LP-050926</t>
-  </si>
-  <si>
-    <t>LP-050961</t>
-  </si>
-  <si>
-    <t>LP-050962</t>
-  </si>
-  <si>
-    <t>LP-050993</t>
-  </si>
-  <si>
-    <t>LP-050994</t>
-  </si>
-  <si>
-    <t>LP-050995</t>
-  </si>
-  <si>
-    <t>LP-050996</t>
-  </si>
-  <si>
-    <t>LP-050997</t>
-  </si>
-  <si>
-    <t>LP-050998</t>
-  </si>
-  <si>
-    <t>LP-050999</t>
-  </si>
-  <si>
-    <t>LP-051026</t>
-  </si>
-  <si>
-    <t>LP-051105</t>
-  </si>
-  <si>
-    <t>LP-051107</t>
-  </si>
-  <si>
-    <t>LP-051119</t>
-  </si>
-  <si>
-    <t>LP-051128</t>
-  </si>
-  <si>
-    <t>LP-051129</t>
-  </si>
-  <si>
-    <t>LP-051251</t>
-  </si>
-  <si>
-    <t>LP-051259</t>
-  </si>
-  <si>
-    <t>LP-051350</t>
-  </si>
-  <si>
-    <t>LP-051453</t>
-  </si>
-  <si>
-    <t>LP-051500</t>
-  </si>
-  <si>
-    <t>LP-051537</t>
-  </si>
-  <si>
-    <t>LP-048392</t>
-  </si>
-  <si>
-    <t>LP-050347</t>
-  </si>
-  <si>
-    <t>LP-050370</t>
-  </si>
-  <si>
-    <t>LP-050599</t>
-  </si>
-  <si>
-    <t>LP-050982</t>
+    <t>LP-047255</t>
+  </si>
+  <si>
+    <t>LP-047649</t>
+  </si>
+  <si>
+    <t>LP-048205</t>
+  </si>
+  <si>
+    <t>LP-048206</t>
+  </si>
+  <si>
+    <t>LP-049726</t>
+  </si>
+  <si>
+    <t>LP-050249</t>
+  </si>
+  <si>
+    <t>LP-050405</t>
+  </si>
+  <si>
+    <t>LP-050889</t>
+  </si>
+  <si>
+    <t>LP-050890</t>
+  </si>
+  <si>
+    <t>LP-050891</t>
+  </si>
+  <si>
+    <t>LP-050392</t>
+  </si>
+  <si>
+    <t>LP-050936</t>
+  </si>
+  <si>
+    <t>LP-051091</t>
+  </si>
+  <si>
+    <t>LP-051143</t>
+  </si>
+  <si>
+    <t>LP-051195</t>
+  </si>
+  <si>
+    <t>LP-051232</t>
+  </si>
+  <si>
+    <t>LP-051254</t>
+  </si>
+  <si>
+    <t>LP-051262</t>
+  </si>
+  <si>
+    <t>LP-051275</t>
+  </si>
+  <si>
+    <t>LP-051276</t>
+  </si>
+  <si>
+    <t>LP-051403</t>
+  </si>
+  <si>
+    <t>LP-051459</t>
+  </si>
+  <si>
+    <t>LP-051531</t>
+  </si>
+  <si>
+    <t>LP-051595</t>
+  </si>
+  <si>
+    <t>LP-051596</t>
+  </si>
+  <si>
+    <t>LP-051611</t>
+  </si>
+  <si>
+    <t>LP-051717</t>
+  </si>
+  <si>
+    <t>LP-051760</t>
+  </si>
+  <si>
+    <t>LP-051891</t>
+  </si>
+  <si>
+    <t>LP-051892</t>
+  </si>
+  <si>
+    <t>LP-051917</t>
+  </si>
+  <si>
+    <t>LP-051924</t>
+  </si>
+  <si>
+    <t>LP-051925</t>
+  </si>
+  <si>
+    <t>LP-051927</t>
+  </si>
+  <si>
+    <t>LP-051929</t>
+  </si>
+  <si>
+    <t>LP-052010</t>
+  </si>
+  <si>
+    <t>LP-052022</t>
+  </si>
+  <si>
+    <t>LP-052041</t>
+  </si>
+  <si>
+    <t>LP-052087</t>
+  </si>
+  <si>
+    <t>LP-046386</t>
+  </si>
+  <si>
+    <t>LP-049057</t>
+  </si>
+  <si>
+    <t>LP-050616</t>
+  </si>
+  <si>
+    <t>LP-052042</t>
   </si>
 </sst>
 </file>
@@ -574,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -587,137 +527,137 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -757,147 +697,47 @@
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs - deitado.xlsx
+++ b/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0844059-5FF2-40C7-8BD1-A311CD41F948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2CDC29-B8BF-4D09-8581-0B218FDF7C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,138 +20,174 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-047255</t>
-  </si>
-  <si>
-    <t>LP-047649</t>
-  </si>
-  <si>
-    <t>LP-048205</t>
-  </si>
-  <si>
-    <t>LP-048206</t>
-  </si>
-  <si>
-    <t>LP-049726</t>
-  </si>
-  <si>
-    <t>LP-050249</t>
-  </si>
-  <si>
-    <t>LP-050405</t>
-  </si>
-  <si>
-    <t>LP-050889</t>
-  </si>
-  <si>
-    <t>LP-050890</t>
-  </si>
-  <si>
-    <t>LP-050891</t>
-  </si>
-  <si>
-    <t>LP-050392</t>
-  </si>
-  <si>
-    <t>LP-050936</t>
-  </si>
-  <si>
-    <t>LP-051091</t>
-  </si>
-  <si>
-    <t>LP-051143</t>
-  </si>
-  <si>
-    <t>LP-051195</t>
-  </si>
-  <si>
-    <t>LP-051232</t>
-  </si>
-  <si>
-    <t>LP-051254</t>
-  </si>
-  <si>
-    <t>LP-051262</t>
-  </si>
-  <si>
-    <t>LP-051275</t>
-  </si>
-  <si>
-    <t>LP-051276</t>
-  </si>
-  <si>
-    <t>LP-051403</t>
-  </si>
-  <si>
-    <t>LP-051459</t>
-  </si>
-  <si>
-    <t>LP-051531</t>
-  </si>
-  <si>
-    <t>LP-051595</t>
-  </si>
-  <si>
-    <t>LP-051596</t>
-  </si>
-  <si>
-    <t>LP-051611</t>
-  </si>
-  <si>
-    <t>LP-051717</t>
-  </si>
-  <si>
-    <t>LP-051760</t>
-  </si>
-  <si>
-    <t>LP-051891</t>
-  </si>
-  <si>
-    <t>LP-051892</t>
-  </si>
-  <si>
-    <t>LP-051917</t>
-  </si>
-  <si>
-    <t>LP-051924</t>
-  </si>
-  <si>
-    <t>LP-051925</t>
-  </si>
-  <si>
-    <t>LP-051927</t>
-  </si>
-  <si>
-    <t>LP-051929</t>
-  </si>
-  <si>
-    <t>LP-052010</t>
-  </si>
-  <si>
-    <t>LP-052022</t>
-  </si>
-  <si>
-    <t>LP-052041</t>
-  </si>
-  <si>
-    <t>LP-052087</t>
-  </si>
-  <si>
-    <t>LP-046386</t>
-  </si>
-  <si>
-    <t>LP-049057</t>
-  </si>
-  <si>
-    <t>LP-050616</t>
-  </si>
-  <si>
-    <t>LP-052042</t>
+    <t>LP-044462</t>
+  </si>
+  <si>
+    <t>LP-045222</t>
+  </si>
+  <si>
+    <t>LP-046519</t>
+  </si>
+  <si>
+    <t>LP-047092</t>
+  </si>
+  <si>
+    <t>LP-047257</t>
+  </si>
+  <si>
+    <t>LP-047258</t>
+  </si>
+  <si>
+    <t>LP-047283</t>
+  </si>
+  <si>
+    <t>LP-047287</t>
+  </si>
+  <si>
+    <t>LP-047294</t>
+  </si>
+  <si>
+    <t>LP-047549</t>
+  </si>
+  <si>
+    <t>LP-047778</t>
+  </si>
+  <si>
+    <t>LP-047989</t>
+  </si>
+  <si>
+    <t>LP-047991</t>
+  </si>
+  <si>
+    <t>LP-048010</t>
+  </si>
+  <si>
+    <t>LP-048343</t>
+  </si>
+  <si>
+    <t>LP-048351</t>
+  </si>
+  <si>
+    <t>LP-048397</t>
+  </si>
+  <si>
+    <t>LP-048426</t>
+  </si>
+  <si>
+    <t>LP-050098</t>
+  </si>
+  <si>
+    <t>LP-050137</t>
+  </si>
+  <si>
+    <t>LP-050248</t>
+  </si>
+  <si>
+    <t>LP-050310</t>
+  </si>
+  <si>
+    <t>LP-050445</t>
+  </si>
+  <si>
+    <t>LP-050895</t>
+  </si>
+  <si>
+    <t>LP-051011</t>
+  </si>
+  <si>
+    <t>LP-051095</t>
+  </si>
+  <si>
+    <t>LP-051172</t>
+  </si>
+  <si>
+    <t>LP-051224</t>
+  </si>
+  <si>
+    <t>LP-051318</t>
+  </si>
+  <si>
+    <t>LP-051319</t>
+  </si>
+  <si>
+    <t>LP-051383</t>
+  </si>
+  <si>
+    <t>LP-051436</t>
+  </si>
+  <si>
+    <t>LP-051626</t>
+  </si>
+  <si>
+    <t>LP-051658</t>
+  </si>
+  <si>
+    <t>LP-051663</t>
+  </si>
+  <si>
+    <t>LP-051756</t>
+  </si>
+  <si>
+    <t>LP-051775</t>
+  </si>
+  <si>
+    <t>LP-051938</t>
+  </si>
+  <si>
+    <t>LP-051967</t>
+  </si>
+  <si>
+    <t>LP-052088</t>
+  </si>
+  <si>
+    <t>LP-052110</t>
+  </si>
+  <si>
+    <t>LP-052133</t>
+  </si>
+  <si>
+    <t>LP-052155</t>
+  </si>
+  <si>
+    <t>LP-052192</t>
+  </si>
+  <si>
+    <t>LP-052253</t>
+  </si>
+  <si>
+    <t>LP-052430</t>
+  </si>
+  <si>
+    <t>LP-052465</t>
+  </si>
+  <si>
+    <t>LP-052479</t>
+  </si>
+  <si>
+    <t>LP-052511</t>
+  </si>
+  <si>
+    <t>LP-052512</t>
+  </si>
+  <si>
+    <t>LP-052516</t>
+  </si>
+  <si>
+    <t>LP-052518</t>
+  </si>
+  <si>
+    <t>LP-052537</t>
+  </si>
+  <si>
+    <t>LP-047454</t>
+  </si>
+  <si>
+    <t>LP-049431</t>
   </si>
 </sst>
 </file>
@@ -514,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -527,22 +563,22 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -552,82 +588,82 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -732,12 +768,77 @@
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
